--- a/data/output/2025/evaluasi_53.xlsx
+++ b/data/output/2025/evaluasi_53.xlsx
@@ -773,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,6 +833,202 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5308</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Lembata</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.03287323243445</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5308</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Lembata</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.097714332954788</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5308</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Lembata</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10.91173130949239</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5308</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Lembata</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5.452563842577725</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5308</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Lembata</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.582796908842477</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5308</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Lembata</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7663214435297689</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5308</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Lembata</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.14767643960596</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -847,7 +1043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,6 +1103,202 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5309</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Flores Timur</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-5.312266274056707</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5309</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Flores Timur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.617473422813508</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5309</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Flores Timur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9.22791206986102</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5309</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Flores Timur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-3.863362621453866</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5309</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Flores Timur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.131941212448956</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5309</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Flores Timur</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8287834917088571</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5309</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Flores Timur</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.218674244314056</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -921,7 +1313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -981,6 +1373,230 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5310</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Sikka</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-4.154392409349886</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5310</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sikka</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.131687240542731</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5310</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sikka</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>19.87660583712812</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5310</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sikka</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.828198851062209</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5310</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sikka</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.79656923667061</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5310</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sikka</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3.681990778875711</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5310</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Sikka</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8422743349396448</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5310</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Sikka</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.56740127438532</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -995,7 +1611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1055,6 +1671,230 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5312</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Ngada</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.248490562695027</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5312</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Ngada</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-3.048535935774809</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5312</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Ngada</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6.541896327108462</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5312</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Ngada</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.299954541769315</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5312</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Ngada</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.284350538617915</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5312</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Ngada</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8824206209887575</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5312</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Ngada</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.474450298489746</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5312</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Ngada</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.229669517908229</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,6 +1969,202 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5313</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Manggarai</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-6.956031241994977</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5313</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Manggarai</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.167556914812126</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5313</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Manggarai</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.71281422213718</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5313</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Manggarai</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.186184281658224</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5313</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Manggarai</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.051451656401834</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5313</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Manggarai</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.271577365621809</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5313</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Manggarai</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.188625183555269</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1143,7 +2179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1357,20 +2393,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-42.87133495807986</v>
+        <v>35.76000599663057</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1385,20 +2421,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-45.97817846278193</v>
+        <v>-3.426863200275883</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q4-25</t>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1413,18 +2449,270 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>12.49772100914041</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5314</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Rote Ndao</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-2.867033046175058</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>5314</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Rote Ndao</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>42.6820858351735</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5314</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Rote Ndao</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.7454080981437182</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5314</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Rote Ndao</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-3.01112189282592</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5314</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Rote Ndao</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.8189053209892698</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5314</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Rote Ndao</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.112817901106887</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>5314</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Rote Ndao</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-42.87133495807986</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>5314</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Rote Ndao</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-45.97817846278193</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>5314</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Rote Ndao</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>-7.688717176744899</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -1441,7 +2729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1501,6 +2789,202 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5315</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Manggarai Barat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-3.323623509421644</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5315</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Manggarai Barat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.616521225678639</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5315</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Manggarai Barat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12.84293984234696</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5315</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Manggarai Barat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.341255540129711</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5315</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Manggarai Barat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.221525740427094</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5315</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Manggarai Barat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8568736047032939</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5315</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Manggarai Barat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.174386491658286</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1515,7 +2999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1575,6 +3059,230 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5316</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Tengah</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-6.609333081513801</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5316</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Tengah</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.807643171051138</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5316</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Tengah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6.429506103150105</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5316</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Tengah</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-3.637979076399388</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5316</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Tengah</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.1944032774329076</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5316</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Tengah</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.056313584809469</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5316</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Tengah</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.5847374255129254</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5316</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Tengah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.13396404832582</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1589,7 +3297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1649,6 +3357,258 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5317</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Barat Daya</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.2311479347949539</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5317</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Barat Daya</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-4.901223963925274</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5317</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Barat Daya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.069493385319042</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5317</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Barat Daya</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.4731884957661</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5317</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Barat Daya</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.866243319008313</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5317</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Barat Daya</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.5106847241015027</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5317</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Barat Daya</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1204488979920779</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5317</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Barat Daya</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8095412636169511</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5317</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Barat Daya</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.013263588770397</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1821,7 +3781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1937,6 +3897,202 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5301</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Barat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>75.50674969623323</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5301</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Barat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7.283518346243794</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5301</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Barat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>17.28328933231607</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5301</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Barat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-3.255769581135856</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5301</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Barat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5.794249041751573</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5301</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Barat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5113200355367848</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5301</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Barat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.795543868897993</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1951,7 +4107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,6 +4251,62 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5319</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Manggarai Timur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>29.32650949169598</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5319</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Manggarai Timur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.77965472417781</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2341,7 +4553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2457,6 +4669,34 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5371</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Kupang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-5.981038796890334</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2471,7 +4711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2587,6 +4827,230 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5311</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Ende</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-4.178793196378903</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5311</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Ende</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-3.076374826663257</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5311</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Ende</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.241779783194906</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5311</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Ende</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1137796905724609</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5311</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Ende</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.3206252207893791</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5311</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Ende</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3061273482901053</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5311</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Ende</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.053539768441571</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>5311</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Ende</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1.058486288115182</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2601,7 +5065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2661,6 +5125,202 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5302</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Timur</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>20.11021878679647</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5302</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Timur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6.323951412203867</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5302</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Timur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.41663991120614</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5302</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Timur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-4.938258724285126</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5302</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Timur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4.783727814001362</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5302</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Timur</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5942381296504066</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5302</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumba Timur</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.162124023579298</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2675,7 +5335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2735,6 +5395,202 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5303</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kupang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>21.80908860623676</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5303</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kupang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5.337602758622912</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5303</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kupang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7.695905717289804</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5303</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kupang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-4.795092490759127</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5303</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kupang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4.078415521481816</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5303</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kupang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5441059342752533</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5303</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kupang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.276939926807533</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2749,7 +5605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2809,6 +5665,202 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5304</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Timor Tengah Selatan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>26.96081999134047</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5304</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Timor Tengah Selatan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3.691185782841323</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5304</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Timor Tengah Selatan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-4.091870332228666</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5304</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Timor Tengah Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.9429813845857263</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5304</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Timor Tengah Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.823384815200596</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5304</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Timor Tengah Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6525481969798035</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5304</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Timor Tengah Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.466046631138079</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2823,7 +5875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2883,6 +5935,202 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5305</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Timor Tengah Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>30.99119444367714</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5305</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Timor Tengah Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4.298187867434234</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5305</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Timor Tengah Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-3.269844256775913</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5305</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Timor Tengah Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-2.563676151139903</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5305</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Timor Tengah Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.752370846046464</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5305</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Timor Tengah Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4487511246977901</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5305</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Timor Tengah Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.28018080134953</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2897,7 +6145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2957,6 +6205,202 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5306</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Belu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>31.69058209816617</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5306</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Belu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5.856291291774034</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5306</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Belu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7.696758244372679</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5306</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Belu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-3.029163148437041</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5306</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Belu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7.239774132955978</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5306</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Belu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4546302618469401</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5306</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Belu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.557590278782941</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2971,7 +6415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3045,20 +6489,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-7.191503967805885</v>
+        <v>-2.782113261824773</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3073,18 +6517,214 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>9.092816572732978</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5307</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Alor</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.106587036800769</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5307</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Alor</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.49554217039724</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5307</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Alor</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.856829100049595</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5307</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Alor</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8917122331567862</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5307</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Alor</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.123224206801824</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5307</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Alor</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-7.191503967805885</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5307</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Alor</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>-7.875125361722711</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
